--- a/dashboard_hanh_dong_v1.xlsx
+++ b/dashboard_hanh_dong_v1.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Dashboard v1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Lộ trình 30-60-90" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
   <si>
     <t>Day 26 - Nhóm NaCl</t>
   </si>
@@ -19,6 +20,9 @@
     <t>Dashboard Hành Động Cho Áp Dụng AI — v1 Trợ lý AI Tuyển dụng &amp; Sàng lọc CV</t>
   </si>
   <si>
+    <t>Lộ trình 30–60–90 Ngày</t>
+  </si>
+  <si>
     <t>Phạm vi: Trợ lý AI Sàng lọc CV · Người dùng: HR/Recruiter · Quy trình: Nhận CV → Sàng lọc → Kiểm chứng/Override → Shortlist</t>
   </si>
   <si>
@@ -46,6 +50,9 @@
     <t>Tỷ lệ HR-label agreement (AI chấm vs HR chấm thủ công)</t>
   </si>
   <si>
+    <t>Giai đoạn</t>
+  </si>
+  <si>
     <t>Product</t>
   </si>
   <si>
@@ -64,9 +71,18 @@
     <t>Review lại rubric; chạy lại eval batch mới</t>
   </si>
   <si>
+    <t>Việc làm</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
     <t>Tỷ lệ CV AI xử lý tự động (confidance score cao, không cần duyệt tay)</t>
   </si>
   <si>
+    <t>Gate — chuyển tiếp khi</t>
+  </si>
+  <si>
     <t>Đo tuần 1 pilot</t>
   </si>
   <si>
@@ -76,6 +92,10 @@
     <t>AI Log</t>
   </si>
   <si>
+    <t>0–30 ngày
+ (Chứng minh vấn đề)</t>
+  </si>
+  <si>
     <t>Calibrate ngưỡng confidence score</t>
   </si>
   <si>
@@ -91,6 +111,11 @@
     <t>Giảm so với AS-IS</t>
   </si>
   <si>
+    <t>Chạy pilot 1–2 HR chính thức + reviewer bổ sung;
+ ghi override log + lý do;
+ hướng dẫn HR đọc evidence và cách override</t>
+  </si>
+  <si>
     <t>HR activity log</t>
   </si>
   <si>
@@ -106,6 +131,9 @@
     <t>Ghi từ tuần 1</t>
   </si>
   <si>
+    <t>HR Lead + IT</t>
+  </si>
+  <si>
     <t>Giảm dần (AI–HR ngày càng đồng thuận)</t>
   </si>
   <si>
@@ -118,6 +146,11 @@
     <t>Tỷ lệ case ambiguous escalate lên HRM</t>
   </si>
   <si>
+    <t>Có baseline data +
+ HR dùng được
+ quy trình mới</t>
+  </si>
+  <si>
     <t>Rủi ro</t>
   </si>
   <si>
@@ -128,13 +161,43 @@
   </si>
   <si>
     <t>Xem lại tiêu chí phân loại score</t>
+  </si>
+  <si>
+    <t>31–60 ngày
+ (Chứng minh chất lượng)</t>
+  </si>
+  <si>
+    <t>Calibrate ngưỡng confidence score lần 1;
+ HRM review override log hàng tuần;
+ theo dõi tỷ lệ override và lý do</t>
+  </si>
+  <si>
+    <t>HRM + IT</t>
+  </si>
+  <si>
+    <t>Tỷ lệ override giảm;
+ ngưỡng score đã điều chỉnh ≥1 lần</t>
+  </si>
+  <si>
+    <t>61–90 ngày
+ (Quyết định mở rộng)</t>
+  </si>
+  <si>
+    <t>So sánh 5 chỉ số với mục tiêu;
+ chạy lại eval batch CV mới;
+ quyết định: mở rộng / sửa / dừng</t>
+  </si>
+  <si>
+    <t>Chỉ số đạt mục tiêu → mở rộng
+ Chưa đạt → sửa
+ Rủi ro cao → dừng</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -174,17 +237,32 @@
       <b/>
       <sz val="11.0"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Monospace"/>
+      <name val="Arial"/>
     </font>
     <font/>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
     <font>
       <b/>
       <sz val="9.0"/>
       <color rgb="FF374151"/>
       <name val="Monospace"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,17 +271,51 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF3D85C6"/>
         <bgColor rgb="FF3D85C6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E75B6"/>
+        <bgColor rgb="FF2E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDFEFE"/>
+        <bgColor rgb="FFFDFEFE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -215,9 +327,6 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
     </border>
     <border>
       <right style="thin">
@@ -248,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -265,16 +374,38 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="6" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="6" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="6" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -285,6 +416,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -519,151 +654,151 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="8"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="9" t="s">
+      <c r="A6" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="C6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="D6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="E6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="F6" s="11" t="s">
         <v>9</v>
       </c>
+      <c r="G6" s="11" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="A7" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="10" t="s">
+      <c r="B7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="C7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="D7" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="E7" s="13" t="s">
         <v>16</v>
       </c>
+      <c r="F7" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>21</v>
+      <c r="G8" s="13" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="10" t="s">
+      <c r="A9" s="13" t="s">
         <v>28</v>
       </c>
+      <c r="B9" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>33</v>
+      <c r="C10" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="10" t="s">
+      <c r="A11" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="10" t="s">
-        <v>38</v>
+      <c r="D11" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -679,4 +814,95 @@
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="20.0"/>
+    <col customWidth="1" min="2" max="2" width="39.88"/>
+    <col customWidth="1" min="3" max="3" width="19.25"/>
+    <col customWidth="1" min="4" max="4" width="29.38"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+    </row>
+    <row r="2" ht="25.5" customHeight="1">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>